--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Home › My Approvals; User Access › Access Requests; User Access › Bulk Request; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › User Access Reports; Administration › Users; Administration › Roles &amp; Permissions; Administration › Second Factor; Administration › Audit Trail; Administration › System Parameters; Administration › Scheduled Jobs; Help › My Profile (every user)</t>
+          <t>Home › My Approvals; User Access › Access Requests; User Access › Bulk Request; User Access › Group Profile Requests; User Access › User Access Matrix; User Access › User Access Reports; Administration › Users; Administration › Identity Synchronisation; Administration › Roles &amp; Permissions; Administration › Second Factor; Administration › Audit Trail; Administration › System Parameters; Administration › Scheduled Jobs; Help › My Profile (every user)</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -867,7 +867,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>BIBS UAT environment (address issued with the passwords). Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -923,7 +923,7 @@
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Environment: BIBS UAT environment (address issued with the passwords). Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
+          <t>Environment: BIBS UAT environment: https://uat.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>BIBS UAT environment (address issued with the passwords). Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_UAT_BRD-11_Business_Unit_Walkthrough_Users_v1.0.xlsx
@@ -867,7 +867,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS DEV environment: https://dev.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -923,7 +923,7 @@
     <row r="29">
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Environment: BIBS UAT environment: https://uat.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
+          <t>Environment: BIBS DEV environment: https://dev.brokerverse.cloud. Passwords: Issued separately by the iorta TechNXT Project Team; no password is written in this workbook.</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>BIBS UAT environment: https://uat.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
+          <t>BIBS DEV environment: https://dev.brokerverse.cloud. Password: Issued separately by the iorta TechNXT Project Team</t>
         </is>
       </c>
     </row>
